--- a/data/payrates.xlsx
+++ b/data/payrates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Kenny-pc\d\Insulpro\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Insulpro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C672C7-EBBC-47A9-8185-024C189610CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC54EC29-AA33-4E0F-A45A-249927C56CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{087E86B0-ED6E-48E9-A68B-D49D65BA4E1B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>name</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>Cellulose - Attic</t>
-  </si>
-  <si>
-    <t>Closed Cell 3/4"</t>
   </si>
   <si>
     <t>Closed Cell &gt; 1"</t>
@@ -514,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D0CAA8-346F-4A16-B548-3CEDBECDD844}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.109375" customWidth="1"/>
@@ -534,7 +531,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -542,7 +539,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -550,12 +547,12 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -566,7 +563,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -574,7 +571,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -582,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -595,7 +592,7 @@
     </row>
     <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
@@ -603,7 +600,7 @@
     </row>
     <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -614,7 +611,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -622,7 +619,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -630,7 +627,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -638,7 +635,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -646,7 +643,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -654,12 +651,12 @@
         <v>5</v>
       </c>
       <c r="B17" s="2">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -670,7 +667,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -678,7 +675,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -686,7 +683,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -694,7 +691,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -702,7 +699,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="21" x14ac:dyDescent="0.4">
@@ -710,20 +707,20 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2">
-        <v>0.22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2">
         <v>1</v>
@@ -731,7 +728,7 @@
     </row>
     <row r="27" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -739,17 +736,9 @@
     </row>
     <row r="28" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2">
         <v>130</v>
       </c>
     </row>
